--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.59443233172918</v>
+        <v>4.321595253905993</v>
       </c>
       <c r="D2" t="n">
-        <v>26.33057298134638</v>
+        <v>4.278718109468787</v>
       </c>
       <c r="E2" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F2" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.37180416504636</v>
+        <v>5.910418176820033</v>
       </c>
       <c r="D3" t="n">
-        <v>36.26168982204467</v>
+        <v>5.89252459608226</v>
       </c>
       <c r="E3" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F3" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.97367177423718</v>
+        <v>8.445721663313542</v>
       </c>
       <c r="D4" t="n">
-        <v>51.91111707267379</v>
+        <v>8.435556524309492</v>
       </c>
       <c r="E4" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F4" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.097494157375019</v>
+        <v>1.315842800573441</v>
       </c>
       <c r="D5" t="n">
-        <v>7.974449723796805</v>
+        <v>1.295848080116981</v>
       </c>
       <c r="E5" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F5" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.30838102182788</v>
+        <v>9.312611916047031</v>
       </c>
       <c r="D6" t="n">
-        <v>55.15621644453807</v>
+        <v>8.962885172237437</v>
       </c>
       <c r="E6" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F6" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.885249871845906</v>
+        <v>0.7938531041749597</v>
       </c>
       <c r="D7" t="n">
-        <v>5.017422624237908</v>
+        <v>0.8153311764386602</v>
       </c>
       <c r="E7" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F7" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.10902927426356</v>
+        <v>4.892717257067829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.22630552841314</v>
+        <v>4.911774648367135</v>
       </c>
       <c r="E8" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F8" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>53.21099407301344</v>
+        <v>8.646786536864685</v>
       </c>
       <c r="D9" t="n">
-        <v>51.40157104554859</v>
+        <v>8.352755294901646</v>
       </c>
       <c r="E9" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F9" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.52638860611399</v>
+        <v>2.360538148493524</v>
       </c>
       <c r="D10" t="n">
-        <v>14.79458474051162</v>
+        <v>2.404120020333139</v>
       </c>
       <c r="E10" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F10" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.00673457903508</v>
+        <v>7.3135943690932</v>
       </c>
       <c r="D11" t="n">
-        <v>43.00370794427401</v>
+        <v>6.988102540944526</v>
       </c>
       <c r="E11" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F11" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.83377188110176</v>
+        <v>6.797987930679036</v>
       </c>
       <c r="D12" t="n">
-        <v>39.61795768189925</v>
+        <v>6.437918123308628</v>
       </c>
       <c r="E12" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F12" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.61274089368021</v>
+        <v>5.137070395223034</v>
       </c>
       <c r="D13" t="n">
-        <v>31.8728803594185</v>
+        <v>5.179343058405506</v>
       </c>
       <c r="E13" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F13" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04956630145642</v>
+        <v>4.395554523986668</v>
       </c>
       <c r="D14" t="n">
-        <v>27.43343198777296</v>
+        <v>4.457932698013106</v>
       </c>
       <c r="E14" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F14" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>26.75655626479767</v>
+        <v>4.347940393029622</v>
       </c>
       <c r="D15" t="n">
-        <v>25.63741700323431</v>
+        <v>4.166080263025576</v>
       </c>
       <c r="E15" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F15" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>13.6555342054176</v>
+        <v>2.219024308380361</v>
       </c>
       <c r="D16" t="n">
-        <v>12.12383259730782</v>
+        <v>1.970122797062521</v>
       </c>
       <c r="E16" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F16" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.02683838745707</v>
+        <v>7.154361237961774</v>
       </c>
       <c r="D17" t="n">
-        <v>44.40207926924579</v>
+        <v>7.215337881252441</v>
       </c>
       <c r="E17" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F17" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>25.08764583087229</v>
+        <v>4.076742447516748</v>
       </c>
       <c r="D18" t="n">
-        <v>25.07722135598545</v>
+        <v>4.075048470347636</v>
       </c>
       <c r="E18" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F18" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>6.097875540796013</v>
+        <v>0.9909047753793521</v>
       </c>
       <c r="D19" t="n">
-        <v>6.574453136948719</v>
+        <v>1.068348634754167</v>
       </c>
       <c r="E19" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F19" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>34.57929969123121</v>
+        <v>5.619136199825072</v>
       </c>
       <c r="D20" t="n">
-        <v>34.55537634040022</v>
+        <v>5.615248655315035</v>
       </c>
       <c r="E20" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F20" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>16.98423646324905</v>
+        <v>2.759938425277972</v>
       </c>
       <c r="D21" t="n">
-        <v>18.16272174029874</v>
+        <v>2.951442282798545</v>
       </c>
       <c r="E21" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F21" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>38.4777507874016</v>
+        <v>6.25263450295276</v>
       </c>
       <c r="D22" t="n">
-        <v>39.2773815082321</v>
+        <v>6.382574495087717</v>
       </c>
       <c r="E22" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F22" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>42.47400032440549</v>
+        <v>6.902025052715893</v>
       </c>
       <c r="D23" t="n">
-        <v>36.844850124441</v>
+        <v>5.987288145221662</v>
       </c>
       <c r="E23" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F23" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>43.7377945143098</v>
+        <v>7.107391608575344</v>
       </c>
       <c r="D24" t="n">
-        <v>29.25562290233069</v>
+        <v>4.754038721628738</v>
       </c>
       <c r="E24" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F24" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>47.68845451369852</v>
+        <v>7.749373858476009</v>
       </c>
       <c r="D25" t="n">
-        <v>15.62515406827544</v>
+        <v>2.539087536094759</v>
       </c>
       <c r="E25" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F25" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>51.48067074070128</v>
+        <v>8.365608995363958</v>
       </c>
       <c r="D26" t="n">
-        <v>3.328819857379928</v>
+        <v>0.5409332268242383</v>
       </c>
       <c r="E26" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F26" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>20.97794781408311</v>
+        <v>3.408916519788506</v>
       </c>
       <c r="D27" t="n">
-        <v>21.18938419761853</v>
+        <v>3.443274932113011</v>
       </c>
       <c r="E27" t="n">
-        <v>15.11095682218121</v>
+        <v>2.455530483604447</v>
       </c>
       <c r="F27" t="n">
-        <v>14.62353717207386</v>
+        <v>2.376324790462002</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
